--- a/out/M01_mobile_network_experience/agent5/agent5_qc_report.xlsx
+++ b/out/M01_mobile_network_experience/agent5/agent5_qc_report.xlsx
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>TC-FT30</t>
+          <t>TC-FT28</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>TC-FT29</t>
+          <t>TC-FT27</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TC-FT16</t>
+          <t>TC-FT15</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>TC-FT32</t>
+          <t>TC-FT30</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>TC-FT37</t>
+          <t>TC-FT35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>TC-FT61</t>
+          <t>TC-FT59</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TC-FT64, TC-FT65, TC-FT66, TC-FT67, TC-FT68</t>
+          <t>TC-FT63, TC-FT64, TC-FT65, TC-FT66, TC-FT67</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1406,11 +1406,11 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>TC-FT16</t>
+          <t>TC-FT15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -1492,11 +1492,11 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>TC-FT29</t>
+          <t>TC-FT27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1537,11 +1537,11 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>TC-FT30</t>
+          <t>TC-FT28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1582,11 +1582,11 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TC-FT32</t>
+          <t>TC-FT30</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TC-FT37</t>
+          <t>TC-FT35</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1709,11 +1709,11 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TC-FT61</t>
+          <t>TC-FT59</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TC-FT64</t>
+          <t>TC-FT63</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1836,11 +1836,11 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TC-FT65</t>
+          <t>TC-FT64</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1877,11 +1877,11 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TC-FT66</t>
+          <t>TC-FT65</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1918,11 +1918,11 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TC-FT67</t>
+          <t>TC-FT66</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1959,11 +1959,11 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TC-FT68</t>
+          <t>TC-FT67</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">

--- a/out/M01_mobile_network_experience/agent5/agent5_qc_report.xlsx
+++ b/out/M01_mobile_network_experience/agent5/agent5_qc_report.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every test judged" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every test judged'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every test judged'!$A$1:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,23 +66,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00A32C36"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00635E7E"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="004338A8"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -106,17 +94,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8E4E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EFEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4E1F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,16 +140,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -727,10 +699,10 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -759,30 +731,30 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>BROKEN</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>NOT PROVEN</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>a respondent taking this journey would meet something wrong</t>
+          <t>nothing on this journey is known to be wrong, but not everything could be proved: COVERAGE_GAP, NEEDS_SAMPLE</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>reject rule R9 fires when its condition holds</t>
+          <t>Q3 presents all 5 items exactly once, with none missing and none repeated</t>
         </is>
       </c>
     </row>
@@ -856,10 +828,10 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -873,7 +845,7 @@
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>WORKING means every test on this journey passed.
 BROKEN means a respondent taking it would meet something wrong: a defect in the survey, a misreading of the questionnaire, or a rule not built yet.
@@ -896,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -960,278 +932,278 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>NOT_BUILT_YET</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>TC-FT18</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Respondent Bot (not built yet)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT28</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Survey Builder (already on the backlog)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>The questionnaire asks for something the survey builder does not emit yet. Expected to fail until it does.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>before the run, Agent 3 already reported REJECT_RULE_NOT_BUILT for R9</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>no action on this test. It will pass once the survey builder emits that rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>TEST_MODEL_GAP</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>TC-FT33</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Respondent Bot (not built yet)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TC-FT38</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Respondent Bot (not built yet)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>TC-FT56</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Respondent Bot (not built yet)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TC-FT60, TC-FT61, TC-FT62, TC-FT63, TC-FT64</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Respondent Bot (not built yet)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS_SAMPLE</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TC-ST01</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>nobody yet (needs a run with many respondents)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>This can only be checked across many respondents, such as the order options are shown in. One run through the survey cannot prove it, so it was never going to run as a single journey.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>the claim is about what happens across many respondents, so it is not a single journey and the bot rightly did not run it</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS_SAMPLE</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT27</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Test Designer</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>The rule is enforced, but by a different mechanism than the test looks for. Nothing is broken; the test needs to learn the other way.</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>the survey was built with LimeSurvey's exclusive option (exclude_all_others), which unticks the other choices when the exclusive one is ticked. The respondent cannot submit both, so there is no error to show</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>check by hand that ticking the exclusive option clears the others. If it does, the rule works and the test should check the end state, not an error message</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT15</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Respondent Bot (not built yet)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT30</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Respondent Bot (not built yet)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT35</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Respondent Bot (not built yet)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TC-ST02</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>nobody yet (needs a run with many respondents)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>This can only be checked across many respondents, such as the order options are shown in. One run through the survey cannot prove it, so it was never going to run as a single journey.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>the claim is about what happens across many respondents, so it is not a single journey and the bot rightly did not run it</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS_SAMPLE</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT59</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Respondent Bot (not built yet)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT63, TC-FT64, TC-FT65, TC-FT66, TC-FT67</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Respondent Bot (not built yet)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>The bot reached the right place but does not yet know how to observe this kind of claim, so nothing was proved either way. Nothing is known to be wrong.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>the bot reached the right place but has no way yet to observe this kind of claim</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_SAMPLE</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>TC-ST01</t>
+          <t>TC-ST03</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1250,80 +1222,6 @@
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_SAMPLE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>TC-ST02</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>nobody yet (needs a run with many respondents)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>This can only be checked across many respondents, such as the order options are shown in. One run through the survey cannot prove it, so it was never going to run as a single journey.</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>the claim is about what happens across many respondents, so it is not a single journey and the bot rightly did not run it</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_SAMPLE</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Q13</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>TC-ST03</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>nobody yet (needs a run with many respondents)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>This can only be checked across many respondents, such as the order options are shown in. One run through the survey cannot prove it, so it was never going to run as a single journey.</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>the claim is about what happens across many respondents, so it is not a single journey and the bot rightly did not run it</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
         </is>
@@ -1343,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1406,11 +1304,11 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>TC-FT15</t>
+          <t>TC-FT18</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -1433,7 +1331,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1447,7 +1345,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -1474,7 +1372,7 @@
           <t>SKIPPED</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>NEEDS_SAMPLE</t>
         </is>
@@ -1492,11 +1390,11 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>TC-FT27</t>
+          <t>TC-FT33</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1511,37 +1409,33 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Q7 rejects an answer breaking ['exclusive_option_id']</t>
+          <t>Q7 presents all 6 items exactly once, with none missing and none repeated</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>TEST_MODEL_GAP</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>it accepted the answer and moved on, when it should have stopped the respondent</t>
-        </is>
-      </c>
+          <t>INCONCLUSIVE</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>check by hand that ticking the exclusive option clears the others. If it does, the rule works and the test should check the end state, not an error message</t>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>TC-FT28</t>
+          <t>TC-ST02</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1556,52 +1450,52 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>reject rule R9 fires when its condition holds</t>
+          <t>Q7 presents its items in a different order to different respondents, proving shuffling is switched on</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>NOT_BUILT_YET</t>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS_SAMPLE</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>it accepted the answer and moved on, when it should have stopped the respondent</t>
+          <t>needs several respondents, so it is not a single journey</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>no action on this test. It will pass once the survey builder emits that rule</t>
+          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TC-FT30</t>
+          <t>TC-FT38</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Q7 presents all 6 items exactly once, with none missing and none repeated</t>
+          <t>Q8's option list is narrowed to what was chosen at Q7</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1609,7 +1503,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1623,16 +1517,16 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>TC-ST02</t>
+          <t>TC-FT56</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1642,83 +1536,83 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Q7 presents its items in a different order to different respondents, proving shuffling is switched on</t>
+          <t>Q13 presents all 5 items exactly once, with none missing and none repeated</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_SAMPLE</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>needs several respondents, so it is not a single journey</t>
-        </is>
-      </c>
+          <t>INCONCLUSIVE</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TC-FT35</t>
+          <t>TC-ST03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Q8's option list is narrowed to what was chosen at Q7</t>
+          <t>Q13 presents its items in a different order to different respondents, proving shuffling is switched on</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>INCONCLUSIVE</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS_SAMPLE</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>needs several respondents, so it is not a single journey</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
+          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TC-FT59</t>
+          <t>TC-FT60</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1728,7 +1622,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Q13 presents all 5 items exactly once, with none missing and none repeated</t>
+          <t>QUOTA_REGION:D1-O1 (North) admits a respondent while below target</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1736,7 +1630,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1750,56 +1644,52 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TC-ST03</t>
+          <t>TC-FT61</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Q13 presents its items in a different order to different respondents, proving shuffling is switched on</t>
+          <t>QUOTA_REGION:D1-O2 (South) admits a respondent while below target</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_SAMPLE</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>needs several respondents, so it is not a single journey</t>
-        </is>
-      </c>
+          <t>INCONCLUSIVE</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>COVERAGE_GAP</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>no action on this test. It needs a run with a sample, which does not exist yet</t>
+          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TC-FT63</t>
+          <t>TC-FT62</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1809,12 +1699,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>QUOTA_REGION:D1-O1 (North) admits a respondent while below target</t>
+          <t>QUOTA_REGION:D1-O3 (East) admits a respondent while below target</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1822,7 +1712,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1836,11 +1726,11 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TC-FT64</t>
+          <t>TC-FT63</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1855,7 +1745,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>QUOTA_REGION:D1-O2 (South) admits a respondent while below target</t>
+          <t>QUOTA_REGION:D1-O4 (West) admits a respondent while below target</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1863,7 +1753,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1877,11 +1767,11 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TC-FT65</t>
+          <t>TC-FT64</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1896,7 +1786,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>QUOTA_REGION:D1-O3 (East) admits a respondent while below target</t>
+          <t>QUOTA_REGION:D1-O5 (Central) admits a respondent while below target</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1904,7 +1794,7 @@
           <t>INCONCLUSIVE</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>COVERAGE_GAP</t>
         </is>
@@ -1916,90 +1806,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT66</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>QUOTA_REGION:D1-O4 (West) admits a respondent while below target</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVE</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>TC-FT67</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>QUOTA_REGION:D1-O5 (Central) admits a respondent while below target</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>INCONCLUSIVE</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE_GAP</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>teach the bot to observe it, or record that this claim cannot be proved by running one respondent through the survey</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:I13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>